--- a/rules/CORE-000206/positive/02/data/unit-test-coreid-CG0371-positive2.xlsx
+++ b/rules/CORE-000206/positive/02/data/unit-test-coreid-CG0371-positive2.xlsx
@@ -1396,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1415,32 +1415,37 @@
           <t>USUBJID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>IDVAR</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>IDVARVAL</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>QNAM</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>QLABEL</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>QVAL</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>QORIG</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>QEVAL</t>
         </is>
@@ -1462,32 +1467,37 @@
           <t>Unique Subject Identifier</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Identifying Variable</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>Identifying Variable Value</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Qualifier Variable Name</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Qualifier Variable Label</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>Qualifier Variable Value</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="J2" s="6" t="inlineStr">
         <is>
           <t>Evaluator</t>
         </is>
@@ -1509,12 +1519,12 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
@@ -1535,6 +1545,11 @@
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
@@ -1550,32 +1565,35 @@
       <c r="C4" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" t="n">
+        <v>50</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>10</t>
         </is>
@@ -1597,24 +1615,24 @@
           <t>003</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n"/>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>RACEOTH</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Other Race</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Antartican</t>
         </is>
       </c>
-      <c r="H5" s="10" t="n"/>
       <c r="I5" s="10" t="n"/>
+      <c r="J5" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1627,7 +1645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1651,27 +1669,32 @@
           <t>IDVAR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>IDVARVAL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>QNAM</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>QLABEL</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>QVAL</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>QORIG</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>QEVAL</t>
         </is>
@@ -1698,27 +1721,32 @@
           <t>Identifying Variable</t>
         </is>
       </c>
-      <c r="E2" s="11" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Identifying Variable Value</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
         <is>
           <t>Qualifier Variable Name</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="G2" s="11" t="inlineStr">
         <is>
           <t>Qualifier Variable Label</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>Data Value</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>Evaluator</t>
         </is>
@@ -1745,7 +1773,7 @@
           <t>Char</t>
         </is>
       </c>
-      <c r="E3" s="11" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
@@ -1766,6 +1794,11 @@
         </is>
       </c>
       <c r="I3" s="11" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="J3" s="11" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
@@ -1784,7 +1817,7 @@
       <c r="D4" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" t="n">
         <v>50</v>
       </c>
       <c r="F4" s="11" t="n">
@@ -1797,6 +1830,9 @@
         <v>50</v>
       </c>
       <c r="I4" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="J4" s="11" t="n">
         <v>50</v>
       </c>
     </row>
@@ -1821,22 +1857,22 @@
           <t>LBSEQ</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>LBCLSIG</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Clinically Significant</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>CRF</t>
         </is>
@@ -1858,22 +1894,22 @@
           <t>S002</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>LBCLSIG</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Clinically Significant</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>CRF</t>
         </is>
@@ -2075,7 +2111,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2104,32 +2140,42 @@
           <t>COSEQ</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>IDVAR</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>IDVARVAL</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>COREF</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>COVAL</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>COEVAL</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>COEVALID</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>CODTC</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>CODY</t>
         </is>
@@ -2161,32 +2207,42 @@
           <t>Sequence Number</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Identifying Variable</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Identifying Variable Value</t>
+        </is>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
         <is>
           <t>Comment Reference</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="I2" s="11" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
+      <c r="J2" s="11" t="inlineStr">
         <is>
           <t>Evaluator</t>
         </is>
       </c>
-      <c r="I2" s="11" t="inlineStr">
+      <c r="K2" s="11" t="inlineStr">
         <is>
           <t>Evaluator Identifier</t>
         </is>
       </c>
-      <c r="J2" s="11" t="inlineStr">
+      <c r="L2" s="11" t="inlineStr">
         <is>
           <t>Date/Time of Comment</t>
         </is>
       </c>
-      <c r="K2" s="11" t="inlineStr">
+      <c r="M2" s="11" t="inlineStr">
         <is>
           <t>Study Day of Comment</t>
         </is>
@@ -2218,12 +2274,12 @@
           <t>Num</t>
         </is>
       </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>Char</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Char</t>
         </is>
@@ -2244,6 +2300,16 @@
         </is>
       </c>
       <c r="K3" s="11" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="L3" s="11" t="inlineStr">
+        <is>
+          <t>Char</t>
+        </is>
+      </c>
+      <c r="M3" s="11" t="inlineStr">
         <is>
           <t>Num</t>
         </is>
@@ -2265,10 +2331,10 @@
       <c r="E4" s="11" t="n">
         <v>8</v>
       </c>
-      <c r="F4" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="G4" s="11" t="n">
+      <c r="F4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G4" t="n">
         <v>50</v>
       </c>
       <c r="H4" s="11" t="n">
@@ -2281,6 +2347,12 @@
         <v>50</v>
       </c>
       <c r="K4" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="L4" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="M4" s="11" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2310,7 +2382,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr">
         <is>
           <t>test comment</t>
         </is>
@@ -2342,7 +2414,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>test comment</t>
         </is>
